--- a/analysis/event_study_results.xlsx
+++ b/analysis/event_study_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">unwinding_start_date</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t xml:space="preserve">its_slope_se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">its_slope_pval</t>
   </si>
   <si>
     <t xml:space="preserve">prepost_intercept</t>
@@ -463,6 +466,9 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -478,48 +484,51 @@
         <v>414652</v>
       </c>
       <c r="E2" t="n">
-        <v>0.956081347797048</v>
+        <v>0.956081347798477</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00122734288362585</v>
+        <v>0.00122734288363732</v>
       </c>
       <c r="G2" t="n">
-        <v>0.502357091314183</v>
+        <v>0.182590580394566</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00217537475742463</v>
+        <v>0.00186237982223893</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.498093356789631</v>
+        <v>0.178940315942978</v>
       </c>
       <c r="K2" t="n">
-        <v>0.506620825838736</v>
+        <v>0.186240844846154</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0122987119584544</v>
+        <v>-0.0122987119584603</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000107160799216651</v>
+        <v>0.000107160799216711</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.971685709411107</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>-0.185310628611174</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.00108199803484851</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>-0.187431344759478</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>-0.183189912462871</v>
       </c>
     </row>
@@ -537,48 +546,51 @@
         <v>409030</v>
       </c>
       <c r="E3" t="n">
-        <v>0.957254319767197</v>
+        <v>0.957254319768164</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00108908799885593</v>
+        <v>0.00108908799887439</v>
       </c>
       <c r="G3" t="n">
-        <v>0.519071326408043</v>
+        <v>0.18404995848512</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00218188459789343</v>
+        <v>0.00183979008895621</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.514794832596172</v>
+        <v>0.180443969910766</v>
       </c>
       <c r="K3" t="n">
-        <v>0.523347820219914</v>
+        <v>0.187655947059474</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0124081988119592</v>
+        <v>-0.0124081988119516</v>
       </c>
       <c r="M3" t="n">
-        <v>0.000101747826579464</v>
+        <v>0.000101747826579407</v>
       </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.971623472140165</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>-0.187771431938459</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0.00106842620310527</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
         <v>-0.189865547296545</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>-0.185677316580373</v>
       </c>
     </row>
@@ -596,48 +608,51 @@
         <v>403084</v>
       </c>
       <c r="E4" t="n">
-        <v>0.95811052993851</v>
+        <v>0.958110529940033</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000991479425323202</v>
+        <v>0.000991479425348979</v>
       </c>
       <c r="G4" t="n">
-        <v>0.537481088769382</v>
+        <v>0.185345888996755</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00219214300369406</v>
+        <v>0.00181402422207316</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.533184488482142</v>
+        <v>0.181790401521492</v>
       </c>
       <c r="K4" t="n">
-        <v>0.541777689056623</v>
+        <v>0.188901376472019</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0125762571347142</v>
+        <v>-0.0125762571347263</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0000965660803451732</v>
+        <v>0.0000965660803451658</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.971695116148551</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>-0.190642035391769</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0.00105498899660924</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
         <v>-0.192709813825123</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>-0.188574256958415</v>
       </c>
     </row>
@@ -655,48 +670,51 @@
         <v>397272</v>
       </c>
       <c r="E5" t="n">
-        <v>0.958819381093147</v>
+        <v>0.958819381094926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000914181393535142</v>
+        <v>0.000914181393574281</v>
       </c>
       <c r="G5" t="n">
-        <v>0.556190383701172</v>
+        <v>0.185990305527113</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00220542692477218</v>
+        <v>0.00179182447945741</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.551867746928618</v>
+        <v>0.182478329547376</v>
       </c>
       <c r="K5" t="n">
-        <v>0.560513020473725</v>
+        <v>0.189502281506849</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0127655199370065</v>
+        <v>-0.0127655199370486</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0000919811768810634</v>
+        <v>0.0000919811768811292</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>0.971798411752701</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-0.193578451615637</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0.00104272607104575</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>-0.195622194714887</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>-0.191534708516388</v>
       </c>
     </row>
@@ -714,48 +732,51 @@
         <v>391772</v>
       </c>
       <c r="E6" t="n">
-        <v>0.95944450571628</v>
+        <v>0.959444505718092</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000848084717592974</v>
+        <v>0.000848084717592217</v>
       </c>
       <c r="G6" t="n">
-        <v>0.574521438042683</v>
+        <v>0.185767078000307</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00222067351764204</v>
+        <v>0.0017742844340667</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.570168917948104</v>
+        <v>0.182289480509536</v>
       </c>
       <c r="K6" t="n">
-        <v>0.578873958137261</v>
+        <v>0.189244675491078</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0129584786680836</v>
+        <v>-0.0129584786680745</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000088005428728597</v>
+        <v>0.0000880054287285757</v>
       </c>
       <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.971884750340865</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-0.196420960166927</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>0.00103186929028551</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
         <v>-0.198443423975887</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-0.194398496357968</v>
       </c>
     </row>
@@ -773,48 +794,51 @@
         <v>385911</v>
       </c>
       <c r="E7" t="n">
-        <v>0.960311685835646</v>
+        <v>0.960311685838068</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000759839746055267</v>
+        <v>0.000759839746046611</v>
       </c>
       <c r="G7" t="n">
-        <v>0.594970557164748</v>
+        <v>0.187002338886236</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00223981865058795</v>
+        <v>0.00175334856749331</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.590580512609596</v>
+        <v>0.183565775693949</v>
       </c>
       <c r="K7" t="n">
-        <v>0.599360601719901</v>
+        <v>0.190438902078523</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0131602651057533</v>
+        <v>-0.0131602651057469</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0000841399385166222</v>
+        <v>0.0000841399385165638</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.971839318803351</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-0.199337368864165</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.00102110392724538</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>-0.201338732561566</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>-0.197336005166764</v>
       </c>
     </row>
@@ -832,48 +856,51 @@
         <v>380428</v>
       </c>
       <c r="E8" t="n">
-        <v>0.960886545768113</v>
+        <v>0.960886545771231</v>
       </c>
       <c r="F8" t="n">
-        <v>0.000703097855702262</v>
+        <v>0.000703097855663892</v>
       </c>
       <c r="G8" t="n">
-        <v>0.61470360573665</v>
+        <v>0.186587583401236</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00226068603730844</v>
+        <v>0.00173760976762004</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.610272661103525</v>
+        <v>0.183181868256701</v>
       </c>
       <c r="K8" t="n">
-        <v>0.619134550369774</v>
+        <v>0.189993298545771</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0133786256979907</v>
+        <v>-0.0133786256979637</v>
       </c>
       <c r="M8" t="n">
-        <v>0.000080844314662263</v>
+        <v>0.0000808443146622226</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.971884425086023</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-0.202277561228812</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.00101162875031754</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>-0.204260353579434</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-0.200294768878189</v>
       </c>
     </row>
@@ -891,48 +918,51 @@
         <v>374846</v>
       </c>
       <c r="E9" t="n">
-        <v>0.96130279032127</v>
+        <v>0.961302790323096</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00066340147213547</v>
+        <v>0.000663401472157392</v>
       </c>
       <c r="G9" t="n">
-        <v>0.635284420440916</v>
+        <v>0.185754714302392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0022848065894268</v>
+        <v>0.0017214435225481</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.63080619952564</v>
+        <v>0.182380684998197</v>
       </c>
       <c r="K9" t="n">
-        <v>0.639762641356193</v>
+        <v>0.189128743606586</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0136221123072167</v>
+        <v>-0.0136221123072419</v>
       </c>
       <c r="M9" t="n">
-        <v>0.000077773454204724</v>
+        <v>0.0000777734542047872</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.971998749488858</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-0.205462625311896</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>0.00100253505260204</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>-0.207427594014996</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-0.203497656608796</v>
       </c>
     </row>
@@ -950,48 +980,51 @@
         <v>369243</v>
       </c>
       <c r="E10" t="n">
-        <v>0.961571129067637</v>
+        <v>0.961571129070567</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00063856658244011</v>
+        <v>0.00063856658243244</v>
       </c>
       <c r="G10" t="n">
-        <v>0.656436904909655</v>
+        <v>0.184349611285429</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00231206599854151</v>
+        <v>0.00170591357817394</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.651905255552514</v>
+        <v>0.181006020672208</v>
       </c>
       <c r="K10" t="n">
-        <v>0.660968554266797</v>
+        <v>0.18769320189865</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0138849204006957</v>
+        <v>-0.0138849204006999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0000749669861911141</v>
+        <v>0.0000749669861911226</v>
       </c>
       <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.972175392241158</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-0.208851510668649</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>0.000993928025875478</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>-0.210799609599365</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-0.206903411737934</v>
       </c>
     </row>
@@ -1009,48 +1042,51 @@
         <v>363924</v>
       </c>
       <c r="E11" t="n">
-        <v>0.961837185321964</v>
+        <v>0.961837185324246</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00061469334855786</v>
+        <v>0.000614693348549787</v>
       </c>
       <c r="G11" t="n">
-        <v>0.676988163362251</v>
+        <v>0.182110986541844</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0023405432071796</v>
+        <v>0.00169326210539583</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.672400698676179</v>
+        <v>0.178792192815268</v>
       </c>
       <c r="K11" t="n">
-        <v>0.681575628048323</v>
+        <v>0.18542978026842</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0141393479091666</v>
+        <v>-0.0141393479091699</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0000725249453231893</v>
+        <v>0.0000725249453231718</v>
       </c>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.972328216058719</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-0.212142023328</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>0.000986245999458083</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>-0.214075065486938</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-0.210208981169063</v>
       </c>
     </row>
@@ -1068,48 +1104,51 @@
         <v>358342</v>
       </c>
       <c r="E12" t="n">
-        <v>0.961959317223476</v>
+        <v>0.961959317225523</v>
       </c>
       <c r="F12" t="n">
-        <v>0.000603998297570437</v>
+        <v>0.000603998297580855</v>
       </c>
       <c r="G12" t="n">
-        <v>0.698832521869522</v>
+        <v>0.179675420369277</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00237339482710349</v>
+        <v>0.00167891712913582</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.694180668008399</v>
+        <v>0.176384742796171</v>
       </c>
       <c r="K12" t="n">
-        <v>0.703484375730645</v>
+        <v>0.182966097942383</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0144210305972224</v>
+        <v>-0.0144210305972342</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0000701898682403658</v>
+        <v>0.0000701898682404027</v>
       </c>
       <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.972560741573352</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-0.215814393103398</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>0.000978611787035216</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>-0.217732472205987</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>-0.213896314000809</v>
       </c>
     </row>
@@ -1127,48 +1166,51 @@
         <v>352902</v>
       </c>
       <c r="E13" t="n">
-        <v>0.962334528961116</v>
+        <v>0.962334528962916</v>
       </c>
       <c r="F13" t="n">
-        <v>0.000572298434944752</v>
+        <v>0.000572298434959852</v>
       </c>
       <c r="G13" t="n">
-        <v>0.720866122933433</v>
+        <v>0.177474447494505</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00240799975990469</v>
+        <v>0.00166601390838548</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.71614644340402</v>
+        <v>0.174209060234069</v>
       </c>
       <c r="K13" t="n">
-        <v>0.725585802462846</v>
+        <v>0.180739834754941</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0146862614983486</v>
+        <v>-0.0146862614983615</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0000681145460031183</v>
+        <v>0.0000681145460031487</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.972650843534987</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-0.219285886682022</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>0.000971692910268384</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>-0.221190404786148</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-0.217381368577896</v>
       </c>
     </row>
@@ -1186,48 +1228,51 @@
         <v>347062</v>
       </c>
       <c r="E14" t="n">
-        <v>0.96276734272904</v>
+        <v>0.9627673427337</v>
       </c>
       <c r="F14" t="n">
-        <v>0.000536601783373917</v>
+        <v>0.000536601783310219</v>
       </c>
       <c r="G14" t="n">
-        <v>0.74525131328906</v>
+        <v>0.176087455996174</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00244841511790901</v>
+        <v>0.00165104803737534</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.740452419657958</v>
+        <v>0.172851401842918</v>
       </c>
       <c r="K14" t="n">
-        <v>0.750050206920162</v>
+        <v>0.179323510149429</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0149779962445541</v>
+        <v>-0.014977996244526</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0000661110283331112</v>
+        <v>0.0000661110283330639</v>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.972713286976378</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-0.223077775156532</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>0.000964743396414059</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>-0.224968672213504</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>-0.221186878099561</v>
       </c>
     </row>
@@ -1245,48 +1290,51 @@
         <v>341161</v>
       </c>
       <c r="E15" t="n">
-        <v>0.963141838402927</v>
+        <v>0.963141838406138</v>
       </c>
       <c r="F15" t="n">
-        <v>0.000506429314118609</v>
+        <v>0.000506429314095451</v>
       </c>
       <c r="G15" t="n">
-        <v>0.770574601122952</v>
+        <v>0.174445043070367</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0024929197413126</v>
+        <v>0.00163689620007336</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.765688478429979</v>
+        <v>0.171236726518223</v>
       </c>
       <c r="K15" t="n">
-        <v>0.775460723815925</v>
+        <v>0.177653359622511</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0152853732834028</v>
+        <v>-0.0152853732833984</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0000643129045432887</v>
+        <v>0.0000643129045433155</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.972788723662458</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>-0.227061632924672</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>0.000958165547512892</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>-0.228939637397797</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>-0.225183628451546</v>
       </c>
     </row>
@@ -1304,48 +1352,51 @@
         <v>335042</v>
       </c>
       <c r="E16" t="n">
-        <v>0.963323026177791</v>
+        <v>0.963323026180721</v>
       </c>
       <c r="F16" t="n">
-        <v>0.000492356045718173</v>
+        <v>0.000492356045694504</v>
       </c>
       <c r="G16" t="n">
-        <v>0.797262527419287</v>
+        <v>0.172355597049811</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00254337859197418</v>
+        <v>0.00162300914274129</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.792277505379018</v>
+        <v>0.169174499130039</v>
       </c>
       <c r="K16" t="n">
-        <v>0.802247549459556</v>
+        <v>0.175536694969584</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0156226732592459</v>
+        <v>-0.0156226732592288</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0000626822204998782</v>
+        <v>0.000062682220499866</v>
       </c>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.972963525582613</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>-0.231504245841738</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>0.000951726521478014</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>-0.233369629823835</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-0.229638861859641</v>
       </c>
     </row>
@@ -1363,48 +1414,51 @@
         <v>328992</v>
       </c>
       <c r="E17" t="n">
-        <v>0.963639945209129</v>
+        <v>0.963639945209994</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000468273898558319</v>
+        <v>0.000468273898613581</v>
       </c>
       <c r="G17" t="n">
-        <v>0.824773212782441</v>
+        <v>0.170375503056765</v>
       </c>
       <c r="H17" t="n">
-        <v>0.00259742679825551</v>
+        <v>0.0016108621491507</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.81968225625786</v>
+        <v>0.16721821324443</v>
       </c>
       <c r="K17" t="n">
-        <v>0.829864169307022</v>
+        <v>0.1735327928691</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0159609197493911</v>
+        <v>-0.0159609197494521</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0000612818968938758</v>
+        <v>0.0000612818968939385</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.973054244795615</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-0.235917779462116</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>0.000945842539351433</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>-0.237771630839245</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-0.234063928084987</v>
       </c>
     </row>
@@ -1422,48 +1476,51 @@
         <v>322867</v>
       </c>
       <c r="E18" t="n">
-        <v>0.963832915008097</v>
+        <v>0.963832915010706</v>
       </c>
       <c r="F18" t="n">
-        <v>0.000453881295722304</v>
+        <v>0.000453881295706233</v>
       </c>
       <c r="G18" t="n">
-        <v>0.853257852469729</v>
+        <v>0.167888305443342</v>
       </c>
       <c r="H18" t="n">
-        <v>0.00265680470053772</v>
+        <v>0.00159980964389466</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.848050515256675</v>
+        <v>0.164752678541308</v>
       </c>
       <c r="K18" t="n">
-        <v>0.858465189682782</v>
+        <v>0.171023932345375</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0163183225482722</v>
+        <v>-0.0163183225482879</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0000600714204916345</v>
+        <v>0.000060071420491662</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.97319792210004</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-0.240645508868782</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>0.000940250881822871</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>-0.242488400597154</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-0.238802617140409</v>
       </c>
     </row>
@@ -1481,48 +1538,51 @@
         <v>316660</v>
       </c>
       <c r="E19" t="n">
-        <v>0.964172238333944</v>
+        <v>0.964172238335314</v>
       </c>
       <c r="F19" t="n">
-        <v>0.000429297308891868</v>
+        <v>0.000429297308912723</v>
       </c>
       <c r="G19" t="n">
-        <v>0.883424137232582</v>
+        <v>0.165860569453396</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00272175111851418</v>
+        <v>0.00158975145817873</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.878089505040294</v>
+        <v>0.162744656595366</v>
       </c>
       <c r="K19" t="n">
-        <v>0.88875876942487</v>
+        <v>0.168976482311427</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.016687524832068</v>
+        <v>-0.0166875248320675</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0000590409261096736</v>
+        <v>0.0000590409261096686</v>
       </c>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.973259338049613</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>-0.245472437264041</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>0.000935044154770549</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>-0.247305123807392</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>-0.243639750720691</v>
       </c>
     </row>
@@ -1540,48 +1600,51 @@
         <v>310388</v>
       </c>
       <c r="E20" t="n">
-        <v>0.964439197744405</v>
+        <v>0.964439197746593</v>
       </c>
       <c r="F20" t="n">
-        <v>0.000410427440106811</v>
+        <v>0.000410427440124246</v>
       </c>
       <c r="G20" t="n">
-        <v>0.914662075452208</v>
+        <v>0.163425791340693</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00279265563352664</v>
+        <v>0.00158085538013252</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.909188470410496</v>
+        <v>0.160327314795634</v>
       </c>
       <c r="K20" t="n">
-        <v>0.920135680493921</v>
+        <v>0.166524267885753</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0170735519116057</v>
+        <v>-0.0170735519116337</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0000581923361165913</v>
+        <v>0.0000581923361166038</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.973347947180251</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>-0.250594490207692</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>0.000930142590709352</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>-0.252417569685483</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>-0.248771410729902</v>
       </c>
     </row>
@@ -1599,48 +1662,51 @@
         <v>303576</v>
       </c>
       <c r="E21" t="n">
-        <v>0.964370971573389</v>
+        <v>0.964370971576041</v>
       </c>
       <c r="F21" t="n">
-        <v>0.000415157873429459</v>
+        <v>0.000415157873439069</v>
       </c>
       <c r="G21" t="n">
-        <v>0.948923936778137</v>
+        <v>0.160707526280927</v>
       </c>
       <c r="H21" t="n">
-        <v>0.00287714823597688</v>
+        <v>0.00157284735288396</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.943284726235622</v>
+        <v>0.157624745469274</v>
       </c>
       <c r="K21" t="n">
-        <v>0.954563147320652</v>
+        <v>0.163790307092579</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0175159202332324</v>
+        <v>-0.0175159202332335</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0000575060451293034</v>
+        <v>0.0000575060451293122</v>
       </c>
       <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.973623617927935</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-0.256732295812542</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>0.000925064211874206</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>-0.258545421667815</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>-0.254919169957268</v>
       </c>
     </row>
@@ -1658,48 +1724,51 @@
         <v>297597</v>
       </c>
       <c r="E22" t="n">
-        <v>0.964562165760746</v>
+        <v>0.964562165762702</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00040219225401501</v>
+        <v>0.00040219225402558</v>
       </c>
       <c r="G22" t="n">
-        <v>0.980729698761436</v>
+        <v>0.156835515832468</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00295711041762275</v>
+        <v>0.00156786520133372</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.974933762342896</v>
+        <v>0.153762500037854</v>
       </c>
       <c r="K22" t="n">
-        <v>0.986525635179977</v>
+        <v>0.159908531627082</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0179107431071317</v>
+        <v>-0.0179107431071186</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0000570752318827271</v>
+        <v>0.0000570752318826998</v>
       </c>
       <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.973730258694673</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-0.262093380626853</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>0.000921053645283147</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>-0.263898645771608</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>-0.260288115482098</v>
       </c>
     </row>
@@ -1717,48 +1786,51 @@
         <v>291556</v>
       </c>
       <c r="E23" t="n">
-        <v>0.964672885303166</v>
+        <v>0.964672885306209</v>
       </c>
       <c r="F23" t="n">
-        <v>0.000394933816252545</v>
+        <v>0.000394933816217352</v>
       </c>
       <c r="G23" t="n">
-        <v>1.01323960302246</v>
+        <v>0.152318533947313</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00304396592160754</v>
+        <v>0.0015637658015816</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.00727342981611</v>
+        <v>0.149253552976213</v>
       </c>
       <c r="K23" t="n">
-        <v>1.01920577622881</v>
+        <v>0.155383514918413</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0183174695548022</v>
+        <v>-0.0183174695547679</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0000568021070301074</v>
+        <v>0.000056802107030116</v>
       </c>
       <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.973878129436419</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>-0.267811370382523</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>0.000917256545557331</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>-0.269609193211815</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>-0.266013547553231</v>
       </c>
     </row>
@@ -1776,48 +1848,51 @@
         <v>285548</v>
       </c>
       <c r="E24" t="n">
-        <v>0.964650322950588</v>
+        <v>0.964650322953603</v>
       </c>
       <c r="F24" t="n">
-        <v>0.000396375081368816</v>
+        <v>0.000396375081368479</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0455411167021</v>
+        <v>0.146652026206988</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00313683850276969</v>
+        <v>0.00156069284537206</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03939291323667</v>
+        <v>0.143593068230059</v>
       </c>
       <c r="K24" t="n">
-        <v>1.05168932016753</v>
+        <v>0.149710984183917</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.0187268560519212</v>
+        <v>-0.0187268560518826</v>
       </c>
       <c r="M24" t="n">
-        <v>0.000056691222472003</v>
+        <v>0.0000566912224719855</v>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.974091274394602</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>-0.273869245165918</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>0.000913685477219763</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>-0.275660068701268</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-0.272078421630567</v>
       </c>
     </row>
@@ -1835,48 +1910,51 @@
         <v>279417</v>
       </c>
       <c r="E25" t="n">
-        <v>0.964741316013776</v>
+        <v>0.964741316015357</v>
       </c>
       <c r="F25" t="n">
-        <v>0.000390588125022561</v>
+        <v>0.000390588125030855</v>
       </c>
       <c r="G25" t="n">
-        <v>1.07946687623535</v>
+        <v>0.14115526615036</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00323862120668657</v>
+        <v>0.00155853250415484</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.07311917867025</v>
+        <v>0.138100542442216</v>
       </c>
       <c r="K25" t="n">
-        <v>1.08581457380046</v>
+        <v>0.144209989858503</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0191492165323425</v>
+        <v>-0.0191492165323377</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0000567401966953712</v>
+        <v>0.0000567401966953611</v>
       </c>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.974247343830644</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-0.280195085011464</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>0.000910368093379265</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>-0.281979406474488</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-0.278410763548441</v>
       </c>
     </row>
@@ -1894,48 +1972,51 @@
         <v>273665</v>
       </c>
       <c r="E26" t="n">
-        <v>0.964879791173668</v>
+        <v>0.964879791174065</v>
       </c>
       <c r="F26" t="n">
-        <v>0.000382026430018495</v>
+        <v>0.000382026430080463</v>
       </c>
       <c r="G26" t="n">
-        <v>1.11162494955365</v>
+        <v>0.134353299930244</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00334067041011009</v>
+        <v>0.0015570338748572</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.10507723554984</v>
+        <v>0.131301513535524</v>
       </c>
       <c r="K26" t="n">
-        <v>1.11817266355747</v>
+        <v>0.137405086324965</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0195454329924131</v>
+        <v>-0.0195454329924373</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0000569298959788885</v>
+        <v>0.0000569298959789241</v>
       </c>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>0.974363785871055</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>-0.286325490867106</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>0.000907519411518385</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>-0.288104228913682</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>-0.28454675282053</v>
       </c>
     </row>
@@ -1953,48 +2034,51 @@
         <v>267632</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9649260202335</v>
+        <v>0.964926020235968</v>
       </c>
       <c r="F27" t="n">
-        <v>0.000379178130066524</v>
+        <v>0.000379178130033718</v>
       </c>
       <c r="G27" t="n">
-        <v>1.14496515363471</v>
+        <v>0.127038452029048</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00345555539899576</v>
+        <v>0.00155655595228027</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1.13819226505267</v>
+        <v>0.123987602362578</v>
       </c>
       <c r="K27" t="n">
-        <v>1.15173804221674</v>
+        <v>0.130089301695517</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.019959347090313</v>
+        <v>-0.0199593470902581</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0000572883853111707</v>
+        <v>0.0000572883853111348</v>
       </c>
       <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0.974533152376467</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-0.293138550827174</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>0.000904701107850123</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>-0.29491176499856</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-0.291365336655787</v>
       </c>
     </row>
@@ -2012,48 +2096,51 @@
         <v>261737</v>
       </c>
       <c r="E28" t="n">
-        <v>0.964980163256379</v>
+        <v>0.964980163256377</v>
       </c>
       <c r="F28" t="n">
-        <v>0.000375984880760883</v>
+        <v>0.00037598488080724</v>
       </c>
       <c r="G28" t="n">
-        <v>1.17722935361881</v>
+        <v>0.118618362343773</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00357589052331791</v>
+        <v>0.00155677209441869</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1.17022060819311</v>
+        <v>0.115567089038712</v>
       </c>
       <c r="K28" t="n">
-        <v>1.18423809904451</v>
+        <v>0.121669635648833</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.0203579036783444</v>
+        <v>-0.0203579036783666</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0000577943589236142</v>
+        <v>0.0000577943589236365</v>
       </c>
       <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
         <v>0.974694209410472</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>-0.300089548997424</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>0.000902157010512128</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>-0.301857776738027</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>-0.29832132125682</v>
       </c>
     </row>
@@ -2071,48 +2158,51 @@
         <v>255746</v>
       </c>
       <c r="E29" t="n">
-        <v>0.965047163611364</v>
+        <v>0.965047163612012</v>
       </c>
       <c r="F29" t="n">
-        <v>0.000372133772416412</v>
+        <v>0.000372133772458319</v>
       </c>
       <c r="G29" t="n">
-        <v>1.20956965950525</v>
+        <v>0.109539814710996</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00370721797248727</v>
+        <v>0.00155802935452073</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1.20230351227918</v>
+        <v>0.106486077176135</v>
       </c>
       <c r="K29" t="n">
-        <v>1.21683580673133</v>
+        <v>0.112593552245856</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.0207552800903908</v>
+        <v>-0.0207552800903677</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0000584722308571686</v>
+        <v>0.0000584722308571539</v>
       </c>
       <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.97485049193838</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>-0.307465664797017</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>0.000899772839158922</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>-0.309229219561769</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>-0.305702110032266</v>
       </c>
     </row>
@@ -2130,48 +2220,51 @@
         <v>249661</v>
       </c>
       <c r="E30" t="n">
-        <v>0.965039220277985</v>
+        <v>0.965039220279148</v>
       </c>
       <c r="F30" t="n">
-        <v>0.000372581957266066</v>
+        <v>0.000372581957293822</v>
       </c>
       <c r="G30" t="n">
-        <v>1.24109134231737</v>
+        <v>0.0992968945490005</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0038509680589421</v>
+        <v>0.00156057498549176</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1.23354344492184</v>
+        <v>0.0962381675774366</v>
       </c>
       <c r="K30" t="n">
-        <v>1.24863923971289</v>
+        <v>0.102355621520564</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.0211443416252769</v>
+        <v>-0.0211443416252658</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0000593377388108358</v>
+        <v>0.0000593377388108357</v>
       </c>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.975046120378793</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>-0.315403645174321</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>0.00089748100438367</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>-0.317162707942913</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-0.313644582405729</v>
       </c>
     </row>
@@ -2189,48 +2282,51 @@
         <v>243664</v>
       </c>
       <c r="E31" t="n">
-        <v>0.965081613995748</v>
+        <v>0.965081613996088</v>
       </c>
       <c r="F31" t="n">
-        <v>0.000370195191316409</v>
+        <v>0.000370195191328173</v>
       </c>
       <c r="G31" t="n">
-        <v>1.27097024653082</v>
+        <v>0.0879515781148261</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00400329595295659</v>
+        <v>0.00156385276480421</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1.26312378646302</v>
+        <v>0.0848864266958099</v>
       </c>
       <c r="K31" t="n">
-        <v>1.27881670659861</v>
+        <v>0.0910167295338424</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.0215094303348356</v>
+        <v>-0.0215094303348299</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0000603648160667688</v>
+        <v>0.0000603648160667742</v>
       </c>
       <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.9752121621122</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>-0.323552499618213</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>0.000895417920589966</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>-0.325307518742569</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>-0.321797480493856</v>
       </c>
     </row>
@@ -2248,48 +2344,51 @@
         <v>237574</v>
       </c>
       <c r="E32" t="n">
-        <v>0.965092472893225</v>
+        <v>0.965092472892748</v>
       </c>
       <c r="F32" t="n">
-        <v>0.000369617725063825</v>
+        <v>0.000369617725081524</v>
       </c>
       <c r="G32" t="n">
-        <v>1.29913561318607</v>
+        <v>0.075338510050408</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00417040091425713</v>
+        <v>0.00156859367012943</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1.29096162739412</v>
+        <v>0.0722640664569543</v>
       </c>
       <c r="K32" t="n">
-        <v>1.30730959897801</v>
+        <v>0.0784129536438617</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.0218535196988693</v>
+        <v>-0.0218535196988847</v>
       </c>
       <c r="M32" t="n">
-        <v>0.000061599790080708</v>
+        <v>0.0000615997900807145</v>
       </c>
       <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.975397336517047</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>-0.332288242079278</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>0.000893439732341664</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>-0.334039383954667</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>-0.330537100203888</v>
       </c>
     </row>
@@ -2307,48 +2406,51 @@
         <v>231771</v>
       </c>
       <c r="E33" t="n">
-        <v>0.965279086197785</v>
+        <v>0.965279086199416</v>
       </c>
       <c r="F33" t="n">
-        <v>0.00035957500429926</v>
+        <v>0.000359575004268387</v>
       </c>
       <c r="G33" t="n">
-        <v>1.32476591907713</v>
+        <v>0.0617587107854747</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00434147446859717</v>
+        <v>0.00157308582098787</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1.31625662911868</v>
+        <v>0.0586754625763385</v>
       </c>
       <c r="K33" t="n">
-        <v>1.33327520903558</v>
+        <v>0.0648419589946109</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.0221580211981137</v>
+        <v>-0.0221580211981186</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0000629534928944524</v>
+        <v>0.0000629534928944532</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>0.97548023105691</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>-0.340810664969105</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>0.000891820534094024</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>-0.34255863321593</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>-0.339062696722281</v>
       </c>
     </row>
@@ -2366,48 +2468,51 @@
         <v>226016</v>
       </c>
       <c r="E34" t="n">
-        <v>0.965474597631625</v>
+        <v>0.965474597633695</v>
       </c>
       <c r="F34" t="n">
-        <v>0.000349290924915001</v>
+        <v>0.00034929092484736</v>
       </c>
       <c r="G34" t="n">
-        <v>1.34692241225883</v>
+        <v>0.0466222460937111</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00452342363323721</v>
+        <v>0.00157801091446767</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000106773347666785</v>
       </c>
       <c r="J34" t="n">
-        <v>1.33805650193768</v>
+        <v>0.0435293447013545</v>
       </c>
       <c r="K34" t="n">
-        <v>1.35578832257997</v>
+        <v>0.0497151474860677</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.022418968382213</v>
+        <v>-0.0224189683821968</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0000644736137493427</v>
+        <v>0.0000644736137493447</v>
       </c>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.975553925173734</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>-0.34967345652699</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>0.000890332654005084</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
         <v>-0.35141850852884</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>-0.34792840452514</v>
       </c>
     </row>
@@ -2425,48 +2530,51 @@
         <v>220217</v>
       </c>
       <c r="E35" t="n">
-        <v>0.965467127259663</v>
+        <v>0.965467127258795</v>
       </c>
       <c r="F35" t="n">
-        <v>0.000349681704156353</v>
+        <v>0.000349681704201697</v>
       </c>
       <c r="G35" t="n">
-        <v>1.36285414139832</v>
+        <v>0.0287538345126316</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00472031804950456</v>
+        <v>0.00158381497180396</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000123477971470567</v>
       </c>
       <c r="J35" t="n">
-        <v>1.35360231802129</v>
+        <v>0.0256495571678959</v>
       </c>
       <c r="K35" t="n">
-        <v>1.37210596477535</v>
+        <v>0.0318581118573674</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.0226118696081786</v>
+        <v>-0.0226118696082</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0000661947069264058</v>
+        <v>0.0000661947069264152</v>
       </c>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>0.975729261958912</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>-0.359332707642137</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>0.000888732174830798</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>-0.361074622704805</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>-0.357590792579469</v>
       </c>
     </row>
@@ -2484,48 +2592,51 @@
         <v>214498</v>
       </c>
       <c r="E36" t="n">
-        <v>0.965481297235251</v>
+        <v>0.96548129723498</v>
       </c>
       <c r="F36" t="n">
-        <v>0.00034893891785639</v>
+        <v>0.000348938917844008</v>
       </c>
       <c r="G36" t="n">
-        <v>1.37288959784073</v>
+        <v>0.00895915130168917</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00492867472337372</v>
+        <v>0.00158975360716415</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.0000000174573198402661</v>
       </c>
       <c r="J36" t="n">
-        <v>1.36322939538292</v>
+        <v>0.00584323423164743</v>
       </c>
       <c r="K36" t="n">
-        <v>1.38254980029854</v>
+        <v>0.0120750683717309</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.0227321741090078</v>
+        <v>-0.0227321741090137</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0000680840011375762</v>
+        <v>0.000068084001137598</v>
       </c>
       <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.975890515183025</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>-0.369339405139831</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>0.000887215140274513</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
         <v>-0.371078346814769</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>-0.367600463464893</v>
       </c>
     </row>
@@ -2543,48 +2654,51 @@
         <v>208902</v>
       </c>
       <c r="E37" t="n">
-        <v>0.965597144695577</v>
+        <v>0.965597144695359</v>
       </c>
       <c r="F37" t="n">
-        <v>0.000343148322518651</v>
+        <v>0.000343148322494018</v>
       </c>
       <c r="G37" t="n">
-        <v>1.37630972499232</v>
+        <v>-0.0125883315289783</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00514592739419464</v>
+        <v>0.00159509531709046</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.00000000000000298147885368215</v>
       </c>
       <c r="J37" t="n">
-        <v>1.3662237072997</v>
+        <v>-0.0157147183504756</v>
       </c>
       <c r="K37" t="n">
-        <v>1.38639574268494</v>
+        <v>-0.00946194470748101</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.0227688205987527</v>
+        <v>-0.0227688205987724</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0000701103767083789</v>
+        <v>0.0000701103767083728</v>
       </c>
       <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
         <v>0.975996467940016</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>-0.379520608438364</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>0.000885849121815454</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>-0.381256872717122</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>-0.377784344159605</v>
       </c>
     </row>
@@ -2602,48 +2716,51 @@
         <v>203294</v>
       </c>
       <c r="E38" t="n">
-        <v>0.965602090777641</v>
+        <v>0.965602090777486</v>
       </c>
       <c r="F38" t="n">
-        <v>0.000342916240512772</v>
+        <v>0.000342916240487993</v>
       </c>
       <c r="G38" t="n">
-        <v>1.3693715002312</v>
+        <v>-0.0371510005313383</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0053776730118638</v>
+        <v>0.00160046293534263</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000385734544867657</v>
       </c>
       <c r="J38" t="n">
-        <v>1.35883126112794</v>
+        <v>-0.0402879078846099</v>
       </c>
       <c r="K38" t="n">
-        <v>1.37991173933445</v>
+        <v>-0.0340140931780667</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.0226858467865197</v>
+        <v>-0.0226858467865276</v>
       </c>
       <c r="M38" t="n">
-        <v>0.0000723227038204306</v>
+        <v>0.0000723227038204344</v>
       </c>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>0.976157723298915</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>-0.390439502389514</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>0.000884354083305509</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>-0.392172836392793</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>-0.388706168386235</v>
       </c>
     </row>
@@ -2661,48 +2778,51 @@
         <v>197946</v>
       </c>
       <c r="E39" t="n">
-        <v>0.965730529688517</v>
+        <v>0.965730529689453</v>
       </c>
       <c r="F39" t="n">
-        <v>0.000336713901461355</v>
+        <v>0.000336713901423353</v>
       </c>
       <c r="G39" t="n">
-        <v>1.35363191272307</v>
+        <v>-0.0634906646869044</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00561129321132064</v>
+        <v>0.00160362692443627</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>1.34263377802888</v>
+        <v>-0.0666337734587995</v>
       </c>
       <c r="K39" t="n">
-        <v>1.36463004741726</v>
+        <v>-0.0603475559150093</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.0224940091652393</v>
+        <v>-0.0224940091652803</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0000745930609573649</v>
+        <v>0.0000745930609574087</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.976248576548249</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>-0.401248323944546</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>0.000883022210017486</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>-0.40297904747618</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>-0.399517600412912</v>
       </c>
     </row>
@@ -2720,48 +2840,51 @@
         <v>192093</v>
       </c>
       <c r="E40" t="n">
-        <v>0.966018200748854</v>
+        <v>0.966018200748</v>
       </c>
       <c r="F40" t="n">
-        <v>0.000322948386064423</v>
+        <v>0.000322948386049804</v>
       </c>
       <c r="G40" t="n">
-        <v>1.32504307701306</v>
+        <v>-0.0922404848179137</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00588306877916375</v>
+        <v>0.00160997862788494</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>1.3135122622059</v>
+        <v>-0.0953960429285682</v>
       </c>
       <c r="K40" t="n">
-        <v>1.33657389182022</v>
+        <v>-0.0890849267072592</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.0221450556536257</v>
+        <v>-0.0221450556536436</v>
       </c>
       <c r="M40" t="n">
-        <v>0.0000772769465527575</v>
+        <v>0.0000772769465527468</v>
       </c>
       <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
         <v>0.976267305096516</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>-0.413529464561236</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>0.000881681240054087</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
         <v>-0.415257559791742</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>-0.41180136933073</v>
       </c>
     </row>
@@ -2779,48 +2902,51 @@
         <v>186067</v>
       </c>
       <c r="E41" t="n">
-        <v>0.966288273921387</v>
+        <v>0.966288273919825</v>
       </c>
       <c r="F41" t="n">
-        <v>0.000310249004238657</v>
+        <v>0.00031024900424011</v>
       </c>
       <c r="G41" t="n">
-        <v>1.27774394188343</v>
+        <v>-0.124799084331519</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00618169169919009</v>
+        <v>0.00161746925628427</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1.26562782615302</v>
+        <v>-0.127969324073836</v>
       </c>
       <c r="K41" t="n">
-        <v>1.28986005761384</v>
+        <v>-0.121628844589202</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.0215775850187156</v>
+        <v>-0.0215775850187612</v>
       </c>
       <c r="M41" t="n">
-        <v>0.0000802670137571051</v>
+        <v>0.0000802670137571754</v>
       </c>
       <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.976293607292292</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>-0.427002222996293</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>0.000880167547222824</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>-0.42872735138885</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>-0.425277094603737</v>
       </c>
     </row>
@@ -2838,48 +2964,51 @@
         <v>179801</v>
       </c>
       <c r="E42" t="n">
-        <v>0.966724603919649</v>
+        <v>0.966724603917952</v>
       </c>
       <c r="F42" t="n">
-        <v>0.00029004462965777</v>
+        <v>0.000290044629684888</v>
       </c>
       <c r="G42" t="n">
-        <v>1.20833731811771</v>
+        <v>-0.16097321869162</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00651480742490788</v>
+        <v>0.00162695873669027</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.19556829556489</v>
+        <v>-0.164162057815533</v>
       </c>
       <c r="K42" t="n">
-        <v>1.22110634067053</v>
+        <v>-0.157784379567707</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.0207471293455579</v>
+        <v>-0.0207471293455315</v>
       </c>
       <c r="M42" t="n">
-        <v>0.000083642645390441</v>
+        <v>0.0000836426453904283</v>
       </c>
       <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.976232992657055</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>-0.441692027919165</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>0.000878644547444731</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
         <v>-0.443414171232157</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>-0.439969884606173</v>
       </c>
     </row>
@@ -2897,48 +3026,51 @@
         <v>173440</v>
       </c>
       <c r="E43" t="n">
-        <v>0.967125498526224</v>
+        <v>0.967125498524881</v>
       </c>
       <c r="F43" t="n">
-        <v>0.000271726315462434</v>
+        <v>0.000271726315464699</v>
       </c>
       <c r="G43" t="n">
-        <v>1.1082665657278</v>
+        <v>-0.202433094190684</v>
       </c>
       <c r="H43" t="n">
-        <v>0.00687884776895087</v>
+        <v>0.00163738870782315</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1.09478402410066</v>
+        <v>-0.205642376058017</v>
       </c>
       <c r="K43" t="n">
-        <v>1.12174910735494</v>
+        <v>-0.199223812323351</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.0195626814913422</v>
+        <v>-0.0195626814913823</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0000873667103408431</v>
+        <v>0.0000873667103409585</v>
       </c>
       <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>0.976180064381971</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>-0.457718348507459</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>0.00087681699388238</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>-0.459436909815468</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>-0.455999787199449</v>
       </c>
     </row>
@@ -2956,48 +3088,51 @@
         <v>166881</v>
       </c>
       <c r="E44" t="n">
-        <v>0.967962194624013</v>
+        <v>0.967962194621862</v>
       </c>
       <c r="F44" t="n">
-        <v>0.000234103690166249</v>
+        <v>0.000234103690203568</v>
       </c>
       <c r="G44" t="n">
-        <v>0.975600197035159</v>
+        <v>-0.247651931727092</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00728585404435843</v>
+        <v>0.00165022256022312</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.961319923108217</v>
+        <v>-0.25088636794513</v>
       </c>
       <c r="K44" t="n">
-        <v>0.989880470962102</v>
+        <v>-0.244417495509055</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.0179890018935398</v>
+        <v>-0.0179890018935508</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0000915659339111473</v>
+        <v>0.0000915659339111705</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>0.975893069263837</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>-0.474733560381382</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>0.000875301381587987</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
         <v>-0.476449151089295</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>-0.47301796967347</v>
       </c>
     </row>
@@ -3015,48 +3150,51 @@
         <v>160221</v>
       </c>
       <c r="E45" t="n">
-        <v>0.968966196157093</v>
+        <v>0.968966196155617</v>
       </c>
       <c r="F45" t="n">
-        <v>0.000189672711143599</v>
+        <v>0.000189672711172756</v>
       </c>
       <c r="G45" t="n">
-        <v>0.79602785549902</v>
+        <v>-0.299155913413295</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00773504781121275</v>
+        <v>0.00166454346238426</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.780867161789043</v>
+        <v>-0.302418418599568</v>
       </c>
       <c r="K45" t="n">
-        <v>0.811188549208997</v>
+        <v>-0.295893408227022</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.0158722285349273</v>
+        <v>-0.0158722285349168</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0000962283191371848</v>
+        <v>0.0000962283191371467</v>
       </c>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>0.975498407316097</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>-0.49307101014554</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>0.000873703645627218</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
         <v>-0.494783469290969</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>-0.49135855100011</v>
       </c>
     </row>
@@ -3074,48 +3212,51 @@
         <v>153824</v>
       </c>
       <c r="E46" t="n">
-        <v>0.970572823393035</v>
+        <v>0.970572823392781</v>
       </c>
       <c r="F46" t="n">
-        <v>0.000119617353303191</v>
+        <v>0.000119617353294907</v>
       </c>
       <c r="G46" t="n">
-        <v>0.582934833972208</v>
+        <v>-0.352108846440925</v>
       </c>
       <c r="H46" t="n">
-        <v>0.00820643407801483</v>
+        <v>0.00167684697115625</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.566850223179299</v>
+        <v>-0.355395466504391</v>
       </c>
       <c r="K46" t="n">
-        <v>0.599019444765117</v>
+        <v>-0.348822226377459</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.0133577668630515</v>
+        <v>-0.0133577668630622</v>
       </c>
       <c r="M46" t="n">
-        <v>0.000101148278632294</v>
+        <v>0.000101148278632288</v>
       </c>
       <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>0.974756745506409</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>-0.510843441981055</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>0.000873053975696789</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
         <v>-0.512554627773421</v>
       </c>
-      <c r="S46" t="n">
+      <c r="T46" t="n">
         <v>-0.509132256188689</v>
       </c>
     </row>
@@ -3133,48 +3274,51 @@
         <v>147271</v>
       </c>
       <c r="E47" t="n">
-        <v>0.97240823417805</v>
+        <v>0.972408234177276</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0000407024679756459</v>
+        <v>0.0000407024679871046</v>
       </c>
       <c r="G47" t="n">
-        <v>0.299502861446649</v>
+        <v>-0.413114204992075</v>
       </c>
       <c r="H47" t="n">
-        <v>0.00872939166452214</v>
+        <v>0.00169043400293112</v>
       </c>
       <c r="I47" t="n">
-        <v>1.03641199436567e-257</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.282393253784185</v>
+        <v>-0.41642745563782</v>
       </c>
       <c r="K47" t="n">
-        <v>0.316612469109112</v>
+        <v>-0.40980095434633</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.0100368600906795</v>
+        <v>-0.0100368600906967</v>
       </c>
       <c r="M47" t="n">
-        <v>0.000106617780773733</v>
+        <v>0.000106617780773831</v>
       </c>
       <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
         <v>0.973854277172505</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>-0.530100924496708</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>0.000872530049600201</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
         <v>-0.531811083393924</v>
       </c>
-      <c r="S47" t="n">
+      <c r="T47" t="n">
         <v>-0.528390765599491</v>
       </c>
     </row>
@@ -3192,48 +3336,51 @@
         <v>141137</v>
       </c>
       <c r="E48" t="n">
-        <v>0.977388103351246</v>
+        <v>0.977388103351053</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.000169668984715397</v>
+        <v>-0.000169668984717739</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0615188663751439</v>
+        <v>-0.453518631168957</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00931511505608523</v>
+        <v>0.00170839924381677</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0000000000400025173903093</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0432612408652169</v>
+        <v>-0.456867093686838</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0797764918850709</v>
+        <v>-0.450170168651077</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.00715329857700355</v>
+        <v>-0.00715329857700166</v>
       </c>
       <c r="M48" t="n">
-        <v>0.000112845024525429</v>
+        <v>0.00011284502452543</v>
       </c>
       <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0.971273104048336</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>-0.542774552985073</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>0.00087923217984895</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
         <v>-0.544497848057577</v>
       </c>
-      <c r="S48" t="n">
+      <c r="T48" t="n">
         <v>-0.541051257912569</v>
       </c>
     </row>
@@ -3251,48 +3398,51 @@
         <v>135229</v>
       </c>
       <c r="E49" t="n">
-        <v>0.985934485091984</v>
+        <v>0.985934485091752</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.000526323426995472</v>
+        <v>-0.000526323426995276</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0784387664693687</v>
+        <v>-0.465017093490612</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0100137029720756</v>
+        <v>0.00173711623951468</v>
       </c>
       <c r="I49" t="n">
-        <v>0.00000000000000476639322495756</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.098065624294637</v>
+        <v>-0.46842184132006</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0588119086441005</v>
+        <v>-0.461612345661163</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.00529559352084168</v>
+        <v>-0.00529559352084737</v>
       </c>
       <c r="M49" t="n">
-        <v>0.000120394744497466</v>
+        <v>0.000120394744497447</v>
       </c>
       <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
         <v>0.966705056584507</v>
       </c>
-      <c r="O49" t="n">
+      <c r="P49" t="n">
         <v>-0.547342345915146</v>
       </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
         <v>0.000895697190320747</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
         <v>-0.549097912408175</v>
       </c>
-      <c r="S49" t="n">
+      <c r="T49" t="n">
         <v>-0.545586779422118</v>
       </c>
     </row>
@@ -3310,48 +3460,51 @@
         <v>129139</v>
       </c>
       <c r="E50" t="n">
-        <v>0.99477464435966</v>
+        <v>0.994774644359567</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.000889791252245731</v>
+        <v>-0.000889791252247219</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.245259496172842</v>
+        <v>-0.477163218370406</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0108169594701961</v>
+        <v>0.0017708977629025</v>
       </c>
       <c r="I50" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000917506322515281</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.266460736734426</v>
+        <v>-0.480634177985695</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.224058255611257</v>
+        <v>-0.473692258755117</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.00313383408375428</v>
+        <v>-0.00313383408375583</v>
       </c>
       <c r="M50" t="n">
-        <v>0.000129081131279032</v>
+        <v>0.000129081131279018</v>
       </c>
       <c r="N50" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000390235721855818</v>
+      </c>
+      <c r="O50" t="n">
         <v>0.961812228229529</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>-0.551680509685776</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>0.000915002183922316</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
         <v>-0.553473913966264</v>
       </c>
-      <c r="S50" t="n">
+      <c r="T50" t="n">
         <v>-0.549887105405289</v>
       </c>
     </row>
@@ -3369,48 +3522,51 @@
         <v>122762</v>
       </c>
       <c r="E51" t="n">
-        <v>1.00582896920173</v>
+        <v>1.00582896920163</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.00133827905357131</v>
+        <v>-0.00133827905357041</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.356896794149269</v>
+        <v>-0.472812290553475</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0118178752488087</v>
+        <v>0.00182127564819698</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000344656796176345</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.380059829636934</v>
+        <v>-0.476381990823941</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.333733758661604</v>
+        <v>-0.469242590283009</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.00154553995205631</v>
+        <v>-0.00154553995205581</v>
       </c>
       <c r="M51" t="n">
-        <v>0.000139959787542225</v>
+        <v>0.000139959787542209</v>
       </c>
       <c r="N51" t="n">
+        <v>0.000000000000000000000000000239254751351369</v>
+      </c>
+      <c r="O51" t="n">
         <v>0.955538688848005</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>-0.551374533806798</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>0.000942574972664007</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
         <v>-0.553221980753219</v>
       </c>
-      <c r="S51" t="n">
+      <c r="T51" t="n">
         <v>-0.549527086860376</v>
       </c>
     </row>
@@ -3428,48 +3584,51 @@
         <v>116723</v>
       </c>
       <c r="E52" t="n">
-        <v>1.01530041118896</v>
+        <v>1.01530041118898</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0017171328028839</v>
+        <v>-0.00171713280288388</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.51499692188048</v>
+        <v>-0.476138974269929</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0128692476801338</v>
+        <v>0.00186362816540745</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.540220647333542</v>
+        <v>-0.479791685474127</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.489773196427418</v>
+        <v>-0.47248626306573</v>
       </c>
       <c r="L52" t="n">
-        <v>0.000511288784349604</v>
+        <v>0.000511288784351237</v>
       </c>
       <c r="M52" t="n">
-        <v>0.000151354760457659</v>
+        <v>0.000151354760457651</v>
       </c>
       <c r="N52" t="n">
+        <v>0.00072998233550631</v>
+      </c>
+      <c r="O52" t="n">
         <v>0.949907008892453</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>-0.552556015502432</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>0.000969410220288879</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>-0.554456059534198</v>
       </c>
-      <c r="S52" t="n">
+      <c r="T52" t="n">
         <v>-0.550655971470666</v>
       </c>
     </row>
@@ -3487,48 +3646,51 @@
         <v>110208</v>
       </c>
       <c r="E53" t="n">
-        <v>1.02663098517205</v>
+        <v>1.02663098517207</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.00216439995686818</v>
+        <v>-0.0021643999568678</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.62948765360392</v>
+        <v>-0.466377224002795</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0142170913811579</v>
+        <v>0.00192849318784767</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.657353152710989</v>
+        <v>-0.470157070650976</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.60162215449685</v>
+        <v>-0.462597377354613</v>
       </c>
       <c r="L53" t="n">
-        <v>0.00211831726754697</v>
+        <v>0.00211831726755082</v>
       </c>
       <c r="M53" t="n">
-        <v>0.00016598802740154</v>
+        <v>0.000165988027401464</v>
       </c>
       <c r="N53" t="n">
+        <v>0.000000000000000000000000000000000000270892775507432</v>
+      </c>
+      <c r="O53" t="n">
         <v>0.943028049019157</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>-0.549844251106352</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>0.00100503041590987</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>-0.551814110721536</v>
       </c>
-      <c r="S53" t="n">
+      <c r="T53" t="n">
         <v>-0.547874391491169</v>
       </c>
     </row>
@@ -3546,48 +3708,51 @@
         <v>104134</v>
       </c>
       <c r="E54" t="n">
-        <v>1.03649549026192</v>
+        <v>1.03649549026132</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.00254850190511925</v>
+        <v>-0.00254850190510374</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.771756187520732</v>
+        <v>-0.46089706747522</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0156579145224196</v>
+        <v>0.00198456575143778</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.802445699984675</v>
+        <v>-0.464786816348038</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.74106667505679</v>
+        <v>-0.457007318602402</v>
       </c>
       <c r="L54" t="n">
-        <v>0.00398537333392326</v>
+        <v>0.00398537333394321</v>
       </c>
       <c r="M54" t="n">
         <v>0.000181597028137583</v>
       </c>
       <c r="N54" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000010422345463915</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.936766155397379</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>-0.547834586450883</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>0.00104046258807155</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
         <v>-0.549873893123503</v>
       </c>
-      <c r="S54" t="n">
+      <c r="T54" t="n">
         <v>-0.545795279778263</v>
       </c>
     </row>
@@ -3605,48 +3770,51 @@
         <v>97719</v>
       </c>
       <c r="E55" t="n">
-        <v>1.04766922208071</v>
+        <v>1.04766922208098</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.00297779530941614</v>
+        <v>-0.00297779530942198</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.855557789153669</v>
+        <v>-0.4427471284007</v>
       </c>
       <c r="H55" t="n">
-        <v>0.01748155263623</v>
+        <v>0.00206309240664384</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.889821632320679</v>
+        <v>-0.446790789517722</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.821293945986658</v>
+        <v>-0.438703467283678</v>
       </c>
       <c r="L55" t="n">
-        <v>0.00522545140192899</v>
+        <v>0.00522545140193711</v>
       </c>
       <c r="M55" t="n">
-        <v>0.000201353690751597</v>
+        <v>0.000201353690751632</v>
       </c>
       <c r="N55" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000213124436401687</v>
+      </c>
+      <c r="O55" t="n">
         <v>0.929550769973705</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>-0.541949586983382</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>0.00108453345383481</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
         <v>-0.544075272552899</v>
       </c>
-      <c r="S55" t="n">
+      <c r="T55" t="n">
         <v>-0.539823901413866</v>
       </c>
     </row>
@@ -3664,48 +3832,51 @@
         <v>91505</v>
       </c>
       <c r="E56" t="n">
-        <v>1.05773469281768</v>
+        <v>1.05773469281763</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.00335946610513815</v>
+        <v>-0.00335946610513566</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.962300965945159</v>
+        <v>-0.427746901656896</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0195696311337473</v>
+        <v>0.00214249276896319</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.0006574429673</v>
+        <v>-0.431946187484064</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.923944488923015</v>
+        <v>-0.423547615829728</v>
       </c>
       <c r="L56" t="n">
-        <v>0.00668192580360085</v>
+        <v>0.00668192580360662</v>
       </c>
       <c r="M56" t="n">
-        <v>0.000223927625766228</v>
+        <v>0.00022392762576615</v>
       </c>
       <c r="N56" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000169657540814941</v>
+      </c>
+      <c r="O56" t="n">
         <v>0.922741398944202</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>-0.536576708480512</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>0.00113041814123244</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
         <v>-0.538792328037328</v>
       </c>
-      <c r="S56" t="n">
+      <c r="T56" t="n">
         <v>-0.534361088923696</v>
       </c>
     </row>
@@ -3723,48 +3894,51 @@
         <v>85611</v>
       </c>
       <c r="E57" t="n">
-        <v>1.06708106082255</v>
+        <v>1.06708106082274</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.00370928079766437</v>
+        <v>-0.00370928079766504</v>
       </c>
       <c r="G57" t="n">
-        <v>-1.04880273875815</v>
+        <v>-0.410000684169413</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0219341869751761</v>
+        <v>0.00221790747126961</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.0917937452295</v>
+        <v>-0.414347782813101</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.00581173228681</v>
+        <v>-0.405653585525724</v>
       </c>
       <c r="L57" t="n">
-        <v>0.00788644511838327</v>
+        <v>0.00788644511838262</v>
       </c>
       <c r="M57" t="n">
-        <v>0.000249450514620668</v>
+        <v>0.000249450514620703</v>
       </c>
       <c r="N57" t="n">
+        <v>3.54003269616654e-219</v>
+      </c>
+      <c r="O57" t="n">
         <v>0.916214109806993</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>-0.530305756904583</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>0.00117865016456753</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>-0.532615911227135</v>
       </c>
-      <c r="S57" t="n">
+      <c r="T57" t="n">
         <v>-0.52799560258203</v>
       </c>
     </row>
@@ -3782,48 +3956,51 @@
         <v>79544</v>
       </c>
       <c r="E58" t="n">
-        <v>1.07657793446402</v>
+        <v>1.07657793446381</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.00406020265369096</v>
+        <v>-0.00406020265368138</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.09515158092875</v>
+        <v>-0.386322103029285</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0248757631586559</v>
+        <v>0.00231173875262828</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.14390807671972</v>
+        <v>-0.390853110984436</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.04639508513778</v>
+        <v>-0.381791095074134</v>
       </c>
       <c r="L58" t="n">
-        <v>0.00864426192561654</v>
+        <v>0.00864426192561262</v>
       </c>
       <c r="M58" t="n">
-        <v>0.000281151954999872</v>
+        <v>0.000281151954999957</v>
       </c>
       <c r="N58" t="n">
+        <v>2.06012726792891e-207</v>
+      </c>
+      <c r="O58" t="n">
         <v>0.909390380573021</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>-0.522133013568907</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>0.00123406991202486</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>-0.524551790596476</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T58" t="n">
         <v>-0.519714236541338</v>
       </c>
     </row>
@@ -3841,48 +4018,51 @@
         <v>73558</v>
       </c>
       <c r="E59" t="n">
-        <v>1.08512068924808</v>
+        <v>1.0851206892485</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.00437194421556984</v>
+        <v>-0.00437194421558059</v>
       </c>
       <c r="G59" t="n">
-        <v>-1.17433708107736</v>
+        <v>-0.366530362982425</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0284311215663423</v>
+        <v>0.00241363940979745</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.23006207934739</v>
+        <v>-0.371261096225628</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.11861208280733</v>
+        <v>-0.361799629739222</v>
       </c>
       <c r="L59" t="n">
-        <v>0.0097326110613684</v>
+        <v>0.00973261106137077</v>
       </c>
       <c r="M59" t="n">
-        <v>0.000319394495380956</v>
+        <v>0.000319394495380817</v>
       </c>
       <c r="N59" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000894338043139947</v>
+      </c>
+      <c r="O59" t="n">
         <v>0.902921282713068</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>-0.514778592588428</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>0.00129350677917697</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
         <v>-0.517313865875614</v>
       </c>
-      <c r="S59" t="n">
+      <c r="T59" t="n">
         <v>-0.512243319301241</v>
       </c>
     </row>
@@ -3900,48 +4080,51 @@
         <v>67892</v>
       </c>
       <c r="E60" t="n">
-        <v>1.09268877556159</v>
+        <v>1.09268877556136</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.00464468216014173</v>
+        <v>-0.00464468216013358</v>
       </c>
       <c r="G60" t="n">
-        <v>-1.26576997509871</v>
+        <v>-0.348138680839458</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0325883458692078</v>
+        <v>0.00250813620890638</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.32964313300236</v>
+        <v>-0.353054627808914</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.20189681719506</v>
+        <v>-0.343222733870001</v>
       </c>
       <c r="L60" t="n">
-        <v>0.0109241820745227</v>
+        <v>0.010924182074534</v>
       </c>
       <c r="M60" t="n">
-        <v>0.000364033420091486</v>
+        <v>0.000364033420091488</v>
       </c>
       <c r="N60" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000107997905645038</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.896933895140065</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>-0.507756967071357</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>0.00135578082484327</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>-0.51041429748805</v>
       </c>
-      <c r="S60" t="n">
+      <c r="T60" t="n">
         <v>-0.505099636654665</v>
       </c>
     </row>
@@ -3959,48 +4142,51 @@
         <v>62242</v>
       </c>
       <c r="E61" t="n">
-        <v>1.09959101994759</v>
+        <v>1.09959101994785</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.00489034244162992</v>
+        <v>-0.00489034244163605</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.42326790143964</v>
+        <v>-0.334013129529205</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0377214730179674</v>
+        <v>0.00260955853526718</v>
       </c>
       <c r="I61" t="n">
-        <v>3.77180522581675e-311</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.49720198855485</v>
+        <v>-0.339127864258329</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.34933381432442</v>
+        <v>-0.328898394800082</v>
       </c>
       <c r="L61" t="n">
-        <v>0.0128147620224688</v>
+        <v>0.0128147620224884</v>
       </c>
       <c r="M61" t="n">
-        <v>0.000419048172751738</v>
+        <v>0.000419048172751651</v>
       </c>
       <c r="N61" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000325783709299279</v>
+      </c>
+      <c r="O61" t="n">
         <v>0.891180597958092</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>-0.501459830624981</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>0.00142460323715449</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
         <v>-0.504252052969804</v>
       </c>
-      <c r="S61" t="n">
+      <c r="T61" t="n">
         <v>-0.498667608280158</v>
       </c>
     </row>
